--- a/vse-loti/339654424/spec-339654424.xlsx
+++ b/vse-loti/339654424/spec-339654424.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -455,35 +455,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>D×s, мм</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -498,20 +503,21 @@
           <t>Труба стальная электросварная круглая</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Погонный метр</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="3" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" s="3" t="n">
         <v>51064.8</v>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -522,20 +528,21 @@
           <t>Труба стальная электросварная круглая</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Погонный метр</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" s="3" t="n">
         <v>63604.8</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -546,20 +553,21 @@
           <t>Труба стальная электросварная круглая</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Погонный метр</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="3" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" s="3" t="n">
         <v>160339.2</v>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -570,20 +578,21 @@
           <t>Труба стальная электросварная круглая</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Погонный метр</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" s="3" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" s="3" t="n">
         <v>30963</v>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -594,20 +603,21 @@
           <t>Труба стальная электросварная круглая</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Погонный метр</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" s="3" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" s="3" t="n">
         <v>37520.4</v>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -618,20 +628,21 @@
           <t>Труба стальная электросварная круглая</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Погонный метр</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" s="3" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" s="3" t="n">
         <v>19756.8</v>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -642,20 +653,21 @@
           <t>Труба стальная электросварная круглая</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Погонный метр</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" s="3" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" s="3" t="n">
         <v>120146.16</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -666,20 +678,21 @@
           <t>Труба стальная электросварная круглая</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Погонный метр</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" s="3" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" s="3" t="n">
         <v>85042.8</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -690,20 +703,21 @@
           <t>Труба стальная электросварная круглая</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Погонный метр</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" s="3" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" s="3" t="n">
         <v>89263.67999999999</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -714,20 +728,21 @@
           <t>Труба стальная электросварная круглая</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Погонный метр</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" s="3" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" s="3" t="n">
         <v>275820.96</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -738,20 +753,21 @@
           <t>Труба стальная электросварная круглая</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Погонный метр</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" s="3" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" s="3" t="n">
         <v>197486.64</v>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -759,7 +775,7 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <v>1131009.24</v>
       </c>
     </row>
@@ -769,14 +785,14 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>1279687</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Источник: preview.txt</t>
+          <t>Источник: Приложение ПИК к проекту государственного (муниципального) контракта 12740481 2026_08_25-16_36 (МСК).txt</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339654424/spec-339654424.xlsx
+++ b/vse-loti/339654424/spec-339654424.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -770,27 +770,52 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>1131009.24</v>
-      </c>
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Труба стальная электросварная круглая</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Погонный метр</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" s="3" t="n">
+        <v>148678.32</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1279687.56</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <v>1279687</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Источник: Приложение ПИК к проекту государственного (муниципального) контракта 12740481 2026_08_25-16_36 (МСК).txt</t>
         </is>
